--- a/Laporan_Siakternak.xlsx
+++ b/Laporan_Siakternak.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Pemasukan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Pengeluaran" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inventaris Ternak" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,6 +567,38 @@
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>05/06/2026 11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 17:03</t>
         </is>
       </c>
     </row>
@@ -580,14 +613,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -613,6 +647,11 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Jumlah</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Tanggal</t>
         </is>
       </c>
@@ -634,7 +673,10 @@
       <c r="D2" s="2" t="n">
         <v>15000000</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>12/02/2026 11:00</t>
         </is>
@@ -657,7 +699,10 @@
       <c r="D3" s="2" t="n">
         <v>5000000</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>18/02/2026 15:30</t>
         </is>
@@ -680,7 +725,10 @@
       <c r="D4" s="2" t="n">
         <v>12000000</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>16/03/2026 10:00</t>
         </is>
@@ -703,7 +751,10 @@
       <c r="D5" s="2" t="n">
         <v>4500000</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>05/04/2026 14:00</t>
         </is>
@@ -726,7 +777,10 @@
       <c r="D6" s="2" t="n">
         <v>18000000</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>22/05/2026 11:00</t>
         </is>
@@ -749,9 +803,458 @@
       <c r="D7" s="2" t="n">
         <v>8000000</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 12:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Nama Barang / Hal</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Tipe Mutasi</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Jumlah</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Masuk</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>01/01/2026 08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Stok awal tahun</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Masuk</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>15/02/2026 09:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Lahir pedet jantan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Masuk</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>10/03/2026 11:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Beli bibit unggul</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>25/04/2026 17:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Sakit kembung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>10/02/2026 10:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>06/06/2026 12:00</t>
+          <t>15/03/2026 14:30</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>02/04/2026 09:15</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>20/05/2026 16:45</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>05/06/2026 11:20</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 16:08</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan dari transaksi ID 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Masuk</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 17:02</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>zzz</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 17:03</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Penjualan otomatis (Transaksi ID 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 17:39</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Acc Pemesanan ID 2 (abdul)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sapi</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Keluar</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>06/06/2026 17:45</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Acc Pemesanan ID 4 (aku)</t>
         </is>
       </c>
     </row>
